--- a/etf_holdings/2026-10-22_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-22_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,16 +451,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,28 +469,28 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00403A(40,000)</t>
+          <t>00980A(33,000)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00993A(-56,000)</t>
+          <t>00993A(-116,000)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -499,24 +499,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00403A(200,000)</t>
+          <t>00980A(30,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00993A(-93,000)</t>
+          <t>00993A(-44,000)、00400A(全數賣出)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -529,24 +529,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00993A(12,000)</t>
+          <t>00993A(553,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00403A(-115,000)</t>
+          <t>00980A(-299,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -559,7 +559,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00981A(547,000)、00993A(6,000)</t>
+          <t>00980A(531,000)、00993A(420,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -571,12 +571,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -589,24 +589,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00400A(新納入)</t>
+          <t>00993A(新納入)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00993A(-116,000)</t>
+          <t>00980A(-165,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -624,19 +624,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00993A(-44,000)、00400A(全數賣出)</t>
+          <t>00980A(-358,000)、00993A(-731,000)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -644,17 +644,317 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>00405A(217)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00993A(全數賣出)</t>
+          <t>00980A(-42,000)、00993A(-23,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>00982A(100,000)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>00980A(-38,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>00980A(-22,000)、00993A(-20,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>00980A(18,000)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>00993A(-12,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>00980A(169,000)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>00993A(-74,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>00993A(58,000)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>00980A(-42,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>00980A(463,000)、00982A(1,200,000)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>00993A(26,000)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>00980A(-14,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>00993A(12,000)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>00980A(-14,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>00980A(62,000)、00993A(16,000)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>00400A(33,000)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>00980A(-16,000)</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-10-22_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-22_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,16 +451,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,28 +469,28 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00980A(33,000)、00400A(新納入)</t>
+          <t>00403A(40,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00993A(-116,000)</t>
+          <t>00993A(-56,000)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -499,24 +499,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00980A(30,000)</t>
+          <t>00403A(200,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00993A(-44,000)、00400A(全數賣出)</t>
+          <t>00993A(-93,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -529,24 +529,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00993A(553,000)</t>
+          <t>00993A(12,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00980A(-299,000)</t>
+          <t>00403A(-115,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -559,7 +559,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00980A(531,000)、00993A(420,000)</t>
+          <t>00981A(547,000)、00993A(6,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -571,12 +571,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -589,24 +589,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00993A(新納入)</t>
+          <t>00400A(新納入)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00980A(-165,000)</t>
+          <t>00993A(-116,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -624,19 +624,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00980A(-358,000)、00993A(-731,000)</t>
+          <t>00993A(-44,000)、00400A(全數賣出)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -644,317 +644,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00405A(217)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00980A(-42,000)、00993A(-23,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>00982A(100,000)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>00980A(-38,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>00980A(-22,000)、00993A(-20,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>00980A(18,000)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>00993A(-12,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3044</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>健鼎</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>00980A(169,000)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>00993A(-74,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>3081</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>聯亞</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>00993A(58,000)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>00980A(-42,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>00980A(463,000)、00982A(1,200,000)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>00993A(26,000)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>00980A(-14,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>00993A(12,000)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>00980A(-14,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>00980A(62,000)、00993A(16,000)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>鴻勁</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>00400A(33,000)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>00980A(-16,000)</t>
+          <t>00993A(全數賣出)</t>
         </is>
       </c>
     </row>
